--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/191.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/191.xlsx
@@ -426,13 +426,13 @@
         <v>5.657448727330541</v>
       </c>
       <c r="E2">
-        <v>-18.80589874897515</v>
+        <v>-17.14306120725462</v>
       </c>
       <c r="F2">
-        <v>-3.702387425692495</v>
+        <v>-3.245227195068102</v>
       </c>
       <c r="G2">
-        <v>-10.2948013035944</v>
+        <v>-10.59273053885558</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>5.539668648958392</v>
       </c>
       <c r="E3">
-        <v>-18.81851054908651</v>
+        <v>-17.32186347497348</v>
       </c>
       <c r="F3">
-        <v>-3.334853234581397</v>
+        <v>-3.183137744758667</v>
       </c>
       <c r="G3">
-        <v>-10.19895438914143</v>
+        <v>-11.28011566190215</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>5.367317707907025</v>
       </c>
       <c r="E4">
-        <v>-16.9613244883788</v>
+        <v>-18.29024141372172</v>
       </c>
       <c r="F4">
-        <v>-3.405477354241874</v>
+        <v>-3.36779657782333</v>
       </c>
       <c r="G4">
-        <v>-9.750372158024641</v>
+        <v>-10.42769322263183</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>5.156629892098202</v>
       </c>
       <c r="E5">
-        <v>-17.33885883792427</v>
+        <v>-19.02776227603294</v>
       </c>
       <c r="F5">
-        <v>-3.112894674103477</v>
+        <v>-2.894455018352651</v>
       </c>
       <c r="G5">
-        <v>-9.992316757671196</v>
+        <v>-10.08796503939182</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>4.920894307722979</v>
       </c>
       <c r="E6">
-        <v>-19.97969279718533</v>
+        <v>-19.12948991614125</v>
       </c>
       <c r="F6">
-        <v>-3.984209613268527</v>
+        <v>-3.310367522522046</v>
       </c>
       <c r="G6">
-        <v>-9.941192002908231</v>
+        <v>-10.01568920917845</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>4.681014269688162</v>
       </c>
       <c r="E7">
-        <v>-19.17396858784458</v>
+        <v>-19.69819379592052</v>
       </c>
       <c r="F7">
-        <v>-3.163610639972474</v>
+        <v>-3.08597770371691</v>
       </c>
       <c r="G7">
-        <v>-10.0551707752798</v>
+        <v>-10.41790062892666</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>4.444498558236446</v>
       </c>
       <c r="E8">
-        <v>-18.73102495973232</v>
+        <v>-20.59505807313964</v>
       </c>
       <c r="F8">
-        <v>-3.727703161889451</v>
+        <v>-2.980283821691513</v>
       </c>
       <c r="G8">
-        <v>-9.333607580085792</v>
+        <v>-9.433695303374577</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>4.232672260860356</v>
       </c>
       <c r="E9">
-        <v>-21.92666491204312</v>
+        <v>-20.72775141851239</v>
       </c>
       <c r="F9">
-        <v>-3.200593931037861</v>
+        <v>-3.047917535027884</v>
       </c>
       <c r="G9">
-        <v>-8.460838527931109</v>
+        <v>-9.540245211556019</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>4.049962448390701</v>
       </c>
       <c r="E10">
-        <v>-21.2896263594881</v>
+        <v>-20.73810351009393</v>
       </c>
       <c r="F10">
-        <v>-3.638032390536404</v>
+        <v>-2.726221054150696</v>
       </c>
       <c r="G10">
-        <v>-8.653856575052778</v>
+        <v>-10.09163643439487</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>3.904992464669457</v>
       </c>
       <c r="E11">
-        <v>-21.78392288284734</v>
+        <v>-21.62586555455762</v>
       </c>
       <c r="F11">
-        <v>-3.271227162739769</v>
+        <v>-2.477021631631716</v>
       </c>
       <c r="G11">
-        <v>-7.668353515649295</v>
+        <v>-9.990999160546567</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>3.802173708489561</v>
       </c>
       <c r="E12">
-        <v>-21.95364556018082</v>
+        <v>-22.19447433638274</v>
       </c>
       <c r="F12">
-        <v>-3.794349461281685</v>
+        <v>-2.593048568639634</v>
       </c>
       <c r="G12">
-        <v>-9.050042801919517</v>
+        <v>-9.379064680885524</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>3.734202554538991</v>
       </c>
       <c r="E13">
-        <v>-22.80673760764179</v>
+        <v>-23.99710134224604</v>
       </c>
       <c r="F13">
-        <v>-3.221882144922406</v>
+        <v>-2.70621349627088</v>
       </c>
       <c r="G13">
-        <v>-8.788698405412832</v>
+        <v>-9.067870089648492</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>3.703262187889839</v>
       </c>
       <c r="E14">
-        <v>-23.93276984049307</v>
+        <v>-23.40237232234468</v>
       </c>
       <c r="F14">
-        <v>-2.650620931501602</v>
+        <v>-2.315495786657631</v>
       </c>
       <c r="G14">
-        <v>-8.341986632525735</v>
+        <v>-7.798908189535993</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>3.69516617934522</v>
       </c>
       <c r="E15">
-        <v>-23.73031535303215</v>
+        <v>-24.2399045331153</v>
       </c>
       <c r="F15">
-        <v>-2.182163426237829</v>
+        <v>-2.181584397423272</v>
       </c>
       <c r="G15">
-        <v>-8.963968617898466</v>
+        <v>-8.413318957260412</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>3.701698885042867</v>
       </c>
       <c r="E16">
-        <v>-24.61382516040265</v>
+        <v>-25.03287655965044</v>
       </c>
       <c r="F16">
-        <v>-2.610232222043307</v>
+        <v>-2.269521395802259</v>
       </c>
       <c r="G16">
-        <v>-7.840293319322422</v>
+        <v>-8.668370006696943</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>3.711643074086139</v>
       </c>
       <c r="E17">
-        <v>-24.01616168934432</v>
+        <v>-25.8583902004047</v>
       </c>
       <c r="F17">
-        <v>-1.798857119777427</v>
+        <v>-1.498779371378501</v>
       </c>
       <c r="G17">
-        <v>-6.501425939602672</v>
+        <v>-7.898863491003208</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>3.709503031087746</v>
       </c>
       <c r="E18">
-        <v>-26.91947505903797</v>
+        <v>-26.07643622387403</v>
       </c>
       <c r="F18">
-        <v>-2.153129148769706</v>
+        <v>-1.64952732807476</v>
       </c>
       <c r="G18">
-        <v>-6.524990402751205</v>
+        <v>-7.541238498577899</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>3.688732177745597</v>
       </c>
       <c r="E19">
-        <v>-26.91832029816602</v>
+        <v>-26.97633910715229</v>
       </c>
       <c r="F19">
-        <v>-1.430760467199828</v>
+        <v>-1.465321611979429</v>
       </c>
       <c r="G19">
-        <v>-7.085118155268193</v>
+        <v>-7.800023843382728</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>3.63505966667058</v>
       </c>
       <c r="E20">
-        <v>-27.94842133763881</v>
+        <v>-27.26945364424677</v>
       </c>
       <c r="F20">
-        <v>-1.880079371989322</v>
+        <v>-1.136794413498756</v>
       </c>
       <c r="G20">
-        <v>-6.333044972384261</v>
+        <v>-7.682959642568559</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>3.542739386355066</v>
       </c>
       <c r="E21">
-        <v>-29.46664206192438</v>
+        <v>-27.61250366422383</v>
       </c>
       <c r="F21">
-        <v>-1.49006494630105</v>
+        <v>-0.8545456167102834</v>
       </c>
       <c r="G21">
-        <v>-8.32660914849582</v>
+        <v>-6.87645446992793</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>3.406098798516584</v>
       </c>
       <c r="E22">
-        <v>-26.98927242891819</v>
+        <v>-28.38312314305711</v>
       </c>
       <c r="F22">
-        <v>-1.376497432112043</v>
+        <v>-0.8263455052167797</v>
       </c>
       <c r="G22">
-        <v>-6.576343585156379</v>
+        <v>-7.329542353523664</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>3.221024466187945</v>
       </c>
       <c r="E23">
-        <v>-28.21442390084936</v>
+        <v>-29.02043340405259</v>
       </c>
       <c r="F23">
-        <v>-0.9684569033714517</v>
+        <v>-0.7268502964665311</v>
       </c>
       <c r="G23">
-        <v>-6.103365943960705</v>
+        <v>-7.044583835685357</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>2.991712771885779</v>
       </c>
       <c r="E24">
-        <v>-28.64188014785539</v>
+        <v>-28.7972158632665</v>
       </c>
       <c r="F24">
-        <v>-0.7929498733729177</v>
+        <v>-0.7490695953118223</v>
       </c>
       <c r="G24">
-        <v>-6.425299944927131</v>
+        <v>-6.925755114098757</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>2.719813333945055</v>
       </c>
       <c r="E25">
-        <v>-29.08026813111594</v>
+        <v>-29.07962055933284</v>
       </c>
       <c r="F25">
-        <v>-0.9376979649707006</v>
+        <v>-0.4209955138004809</v>
       </c>
       <c r="G25">
-        <v>-6.499154905362732</v>
+        <v>-6.885581643979701</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>2.416104911937415</v>
       </c>
       <c r="E26">
-        <v>-27.95140560200986</v>
+        <v>-29.32592878908404</v>
       </c>
       <c r="F26">
-        <v>-0.8509985474914958</v>
+        <v>-0.7222619694224247</v>
       </c>
       <c r="G26">
-        <v>-7.084101817787637</v>
+        <v>-7.110745088287691</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>2.09171159803156</v>
       </c>
       <c r="E27">
-        <v>-30.66856925490721</v>
+        <v>-30.06103823898617</v>
       </c>
       <c r="F27">
-        <v>-0.7533978149914498</v>
+        <v>-0.428601583292986</v>
       </c>
       <c r="G27">
-        <v>-7.812024570962586</v>
+        <v>-7.457736608440862</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>1.760103629946987</v>
       </c>
       <c r="E28">
-        <v>-28.99439920698249</v>
+        <v>-29.61636473380298</v>
       </c>
       <c r="F28">
-        <v>-0.4472423349581832</v>
+        <v>-0.6034252101842105</v>
       </c>
       <c r="G28">
-        <v>-6.998765885421844</v>
+        <v>-6.953686186813588</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>1.439776678533506</v>
       </c>
       <c r="E29">
-        <v>-28.50123480212517</v>
+        <v>-28.46912339293678</v>
       </c>
       <c r="F29">
-        <v>-1.212996759249685</v>
+        <v>-0.3480685327602208</v>
       </c>
       <c r="G29">
-        <v>-7.726804507690667</v>
+        <v>-7.313350475291088</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>1.143754220752405</v>
       </c>
       <c r="E30">
-        <v>-28.36201592570736</v>
+        <v>-29.10327730754891</v>
       </c>
       <c r="F30">
-        <v>-0.7637002203800671</v>
+        <v>-0.5800635926904587</v>
       </c>
       <c r="G30">
-        <v>-7.145340289173076</v>
+        <v>-8.079728525450211</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>0.8896029301229774</v>
       </c>
       <c r="E31">
-        <v>-28.087866637757</v>
+        <v>-29.47073353819031</v>
       </c>
       <c r="F31">
-        <v>-0.7961987303266974</v>
+        <v>-0.243256862018805</v>
       </c>
       <c r="G31">
-        <v>-7.47772899295252</v>
+        <v>-8.442183603817316</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>0.6874848295944272</v>
       </c>
       <c r="E32">
-        <v>-27.10570402412941</v>
+        <v>-28.35848371598138</v>
       </c>
       <c r="F32">
-        <v>-1.038828370974075</v>
+        <v>-0.3516810430038295</v>
       </c>
       <c r="G32">
-        <v>-7.31479387314621</v>
+        <v>-7.514148304430043</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>0.5439431614041217</v>
       </c>
       <c r="E33">
-        <v>-27.41367195596905</v>
+        <v>-27.8129203383813</v>
       </c>
       <c r="F33">
-        <v>-1.253757405671838</v>
+        <v>-0.818469387950962</v>
       </c>
       <c r="G33">
-        <v>-6.92642053375215</v>
+        <v>-7.372427160439383</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>0.4632899716056877</v>
       </c>
       <c r="E34">
-        <v>-27.38050088386286</v>
+        <v>-27.32833739176851</v>
       </c>
       <c r="F34">
-        <v>-0.8665271228243754</v>
+        <v>-0.7937633301624668</v>
       </c>
       <c r="G34">
-        <v>-7.421413302783979</v>
+        <v>-7.167431559556632</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>0.4395744834514236</v>
       </c>
       <c r="E35">
-        <v>-27.8246717284312</v>
+        <v>-27.07679424606444</v>
       </c>
       <c r="F35">
-        <v>-0.9549114396008742</v>
+        <v>-0.8968370860928093</v>
       </c>
       <c r="G35">
-        <v>-7.593624571191326</v>
+        <v>-7.171788237486313</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>0.4686590998344174</v>
       </c>
       <c r="E36">
-        <v>-26.11586564705881</v>
+        <v>-27.69902468861438</v>
       </c>
       <c r="F36">
-        <v>-0.8233128521551308</v>
+        <v>-0.7493578671679966</v>
       </c>
       <c r="G36">
-        <v>-6.608469119069467</v>
+        <v>-7.377677685664667</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>0.5390056117772272</v>
       </c>
       <c r="E37">
-        <v>-27.1975052492129</v>
+        <v>-26.08992201946887</v>
       </c>
       <c r="F37">
-        <v>-1.47487931507293</v>
+        <v>-0.8293036052121768</v>
       </c>
       <c r="G37">
-        <v>-7.492411262419188</v>
+        <v>-6.917591308798914</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>0.6386262262542988</v>
       </c>
       <c r="E38">
-        <v>-25.43072111512031</v>
+        <v>-25.76407567224695</v>
       </c>
       <c r="F38">
-        <v>-0.6520661157091946</v>
+        <v>-0.8419660293313701</v>
       </c>
       <c r="G38">
-        <v>-7.408618044274695</v>
+        <v>-6.825822986450317</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>0.7551428300510848</v>
       </c>
       <c r="E39">
-        <v>-26.08264929021255</v>
+        <v>-25.5833306891788</v>
       </c>
       <c r="F39">
-        <v>-0.7642593683769568</v>
+        <v>-0.857393543841108</v>
       </c>
       <c r="G39">
-        <v>-6.55299099692236</v>
+        <v>-6.660232809121511</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>0.8730247648638897</v>
       </c>
       <c r="E40">
-        <v>-25.41142075889962</v>
+        <v>-25.62997397145781</v>
       </c>
       <c r="F40">
-        <v>-0.9770172521119819</v>
+        <v>-0.578562590956586</v>
       </c>
       <c r="G40">
-        <v>-6.879371060548028</v>
+        <v>-7.016023759318064</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>0.9803776470404437</v>
       </c>
       <c r="E41">
-        <v>-24.75309837850855</v>
+        <v>-25.13646087410189</v>
       </c>
       <c r="F41">
-        <v>-0.5222998769584436</v>
+        <v>-0.5944208565157798</v>
       </c>
       <c r="G41">
-        <v>-5.348521834460403</v>
+        <v>-6.439465769289673</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>1.064517255799107</v>
       </c>
       <c r="E42">
-        <v>-25.96227339414066</v>
+        <v>-25.09688201127485</v>
       </c>
       <c r="F42">
-        <v>-0.9770338194600379</v>
+        <v>-0.9339653414536859</v>
       </c>
       <c r="G42">
-        <v>-6.149793034603444</v>
+        <v>-6.92919477091406</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>1.115548363867917</v>
       </c>
       <c r="E43">
-        <v>-23.13303680226448</v>
+        <v>-24.73217230011911</v>
       </c>
       <c r="F43">
-        <v>-0.5191827304217091</v>
+        <v>-0.7476671692988828</v>
       </c>
       <c r="G43">
-        <v>-6.511715115138728</v>
+        <v>-6.149114372767894</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>1.126152218714496</v>
       </c>
       <c r="E44">
-        <v>-22.87394469038963</v>
+        <v>-23.9458888296933</v>
       </c>
       <c r="F44">
-        <v>-1.010711924588255</v>
+        <v>-0.949594977609707</v>
       </c>
       <c r="G44">
-        <v>-7.328277725127662</v>
+        <v>-6.605923309549768</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>1.092210412198159</v>
       </c>
       <c r="E45">
-        <v>-23.31534863733928</v>
+        <v>-23.63915264278374</v>
       </c>
       <c r="F45">
-        <v>-0.9531014568257573</v>
+        <v>-1.035648268514728</v>
       </c>
       <c r="G45">
-        <v>-7.418900598719671</v>
+        <v>-6.201291881012347</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>1.013338243162928</v>
       </c>
       <c r="E46">
-        <v>-24.52380815407818</v>
+        <v>-22.28200068200299</v>
       </c>
       <c r="F46">
-        <v>-1.313054429466435</v>
+        <v>-1.120097840127929</v>
       </c>
       <c r="G46">
-        <v>-7.054505540666552</v>
+        <v>-6.611458541691428</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>0.8924933752193693</v>
       </c>
       <c r="E47">
-        <v>-22.33525553633319</v>
+        <v>-22.7644688312542</v>
       </c>
       <c r="F47">
-        <v>-0.6804136766003964</v>
+        <v>-0.9092601120325935</v>
       </c>
       <c r="G47">
-        <v>-6.932012045167979</v>
+        <v>-7.179803068236889</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>0.7352048519566226</v>
       </c>
       <c r="E48">
-        <v>-22.23581477559876</v>
+        <v>-22.53607524467734</v>
       </c>
       <c r="F48">
-        <v>-1.155793848249365</v>
+        <v>-0.8745954213276426</v>
       </c>
       <c r="G48">
-        <v>-5.848026877062257</v>
+        <v>-6.942708417805364</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>0.5492853278935651</v>
       </c>
       <c r="E49">
-        <v>-21.83969556872581</v>
+        <v>-21.94136433867202</v>
       </c>
       <c r="F49">
-        <v>-1.311815191831847</v>
+        <v>-0.9725283291562113</v>
       </c>
       <c r="G49">
-        <v>-7.572658886291122</v>
+        <v>-6.604993046253232</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>0.3443758622565041</v>
       </c>
       <c r="E50">
-        <v>-20.00612097149409</v>
+        <v>-22.07446524670546</v>
       </c>
       <c r="F50">
-        <v>-1.629905789404649</v>
+        <v>-0.7912600038712068</v>
       </c>
       <c r="G50">
-        <v>-5.994776739727071</v>
+        <v>-6.856971909429319</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>0.130436972118483</v>
       </c>
       <c r="E51">
-        <v>-21.12293775973976</v>
+        <v>-20.401624305902</v>
       </c>
       <c r="F51">
-        <v>-1.294923952121362</v>
+        <v>-1.013128272302221</v>
       </c>
       <c r="G51">
-        <v>-7.508821636657355</v>
+        <v>-6.887498449846939</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-0.08265053888866933</v>
       </c>
       <c r="E52">
-        <v>-19.2400390236165</v>
+        <v>-21.10562993208245</v>
       </c>
       <c r="F52">
-        <v>-1.294020203284908</v>
+        <v>-0.9248118816527514</v>
       </c>
       <c r="G52">
-        <v>-8.371913964200747</v>
+        <v>-6.790559055366</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-0.2862116902532134</v>
       </c>
       <c r="E53">
-        <v>-18.94907098320165</v>
+        <v>-21.05653221689128</v>
       </c>
       <c r="F53">
-        <v>-1.117992130190013</v>
+        <v>-0.9857979465816566</v>
       </c>
       <c r="G53">
-        <v>-7.748670660977553</v>
+        <v>-8.004426856613948</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-0.4725985751742986</v>
       </c>
       <c r="E54">
-        <v>-19.40813145030721</v>
+        <v>-20.56418293735534</v>
       </c>
       <c r="F54">
-        <v>-1.623456120806452</v>
+        <v>-0.8703657773689483</v>
       </c>
       <c r="G54">
-        <v>-8.942714915536346</v>
+        <v>-7.792588358101525</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-0.6359343969289243</v>
       </c>
       <c r="E55">
-        <v>-19.27312405471654</v>
+        <v>-19.65758244101973</v>
       </c>
       <c r="F55">
-        <v>-0.9184086016291112</v>
+        <v>-1.091084271844877</v>
       </c>
       <c r="G55">
-        <v>-8.565471630245314</v>
+        <v>-7.702991753626689</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-0.7731716333262646</v>
       </c>
       <c r="E56">
-        <v>-20.01920373290225</v>
+        <v>-19.9270719292162</v>
       </c>
       <c r="F56">
-        <v>-0.9923403923289671</v>
+        <v>-0.991568353909558</v>
       </c>
       <c r="G56">
-        <v>-7.523593290853583</v>
+        <v>-7.428842166974102</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-0.8840350780003443</v>
       </c>
       <c r="E57">
-        <v>-18.97464780439698</v>
+        <v>-18.8403513792255</v>
       </c>
       <c r="F57">
-        <v>-1.344359261985631</v>
+        <v>-0.9296404352436697</v>
       </c>
       <c r="G57">
-        <v>-8.791946050586857</v>
+        <v>-7.408849782462444</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-0.9707487142154588</v>
       </c>
       <c r="E58">
-        <v>-18.67796935825846</v>
+        <v>-18.85124688768796</v>
       </c>
       <c r="F58">
-        <v>-0.5932445748038045</v>
+        <v>-0.9168893758123769</v>
       </c>
       <c r="G58">
-        <v>-8.272425449654568</v>
+        <v>-7.922086967961196</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-1.036285022884124</v>
       </c>
       <c r="E59">
-        <v>-18.6396765820496</v>
+        <v>-19.14086091437451</v>
       </c>
       <c r="F59">
-        <v>-0.6851386842659648</v>
+        <v>-1.222349855594695</v>
       </c>
       <c r="G59">
-        <v>-7.75195472215251</v>
+        <v>-7.113357108718176</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-1.084420341310993</v>
       </c>
       <c r="E60">
-        <v>-18.21699334664766</v>
+        <v>-18.89675352299104</v>
       </c>
       <c r="F60">
-        <v>-0.7228070351734668</v>
+        <v>-0.9811309246342842</v>
       </c>
       <c r="G60">
-        <v>-8.325281619734573</v>
+        <v>-7.508195943550433</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-1.119963349809351</v>
       </c>
       <c r="E61">
-        <v>-17.46181143570652</v>
+        <v>-18.73107477294641</v>
       </c>
       <c r="F61">
-        <v>-1.400962434986324</v>
+        <v>-1.258836126218402</v>
       </c>
       <c r="G61">
-        <v>-9.468552037357563</v>
+        <v>-7.896724878584839</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-1.146401573418363</v>
       </c>
       <c r="E62">
-        <v>-17.52635124726384</v>
+        <v>-18.3558227743008</v>
       </c>
       <c r="F62">
-        <v>-1.080378451531096</v>
+        <v>-0.9882035255193864</v>
       </c>
       <c r="G62">
-        <v>-8.88718382466061</v>
+        <v>-8.360783910097716</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-1.168581679319556</v>
       </c>
       <c r="E63">
-        <v>-18.67139854247333</v>
+        <v>-18.68939922665382</v>
       </c>
       <c r="F63">
-        <v>-1.225259910280729</v>
+        <v>-0.8851844418376287</v>
       </c>
       <c r="G63">
-        <v>-8.810703601612367</v>
+        <v>-7.421327228599957</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-1.189277703692734</v>
       </c>
       <c r="E64">
-        <v>-18.66455601824774</v>
+        <v>-18.39414272135371</v>
       </c>
       <c r="F64">
-        <v>-1.383934514654377</v>
+        <v>-0.8258650521231561</v>
       </c>
       <c r="G64">
-        <v>-9.195451893640925</v>
+        <v>-7.904428518054723</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-1.210237043272085</v>
       </c>
       <c r="E65">
-        <v>-18.26245469721066</v>
+        <v>-18.37982821501546</v>
       </c>
       <c r="F65">
-        <v>-1.410269971124179</v>
+        <v>-1.239467239606144</v>
       </c>
       <c r="G65">
-        <v>-8.749011585488049</v>
+        <v>-7.766544296344078</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-1.233491105645739</v>
       </c>
       <c r="E66">
-        <v>-16.99266152851187</v>
+        <v>-18.54835990368493</v>
       </c>
       <c r="F66">
-        <v>-1.028500286195971</v>
+        <v>-1.084231188321516</v>
       </c>
       <c r="G66">
-        <v>-8.137073795281466</v>
+        <v>-7.755748607340514</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-1.257519588605062</v>
       </c>
       <c r="E67">
-        <v>-17.55935023735773</v>
+        <v>-17.90744497737934</v>
       </c>
       <c r="F67">
-        <v>-1.225061102104057</v>
+        <v>-1.229021526656842</v>
       </c>
       <c r="G67">
-        <v>-8.123901134580706</v>
+        <v>-7.713790753175791</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-1.282556687776457</v>
       </c>
       <c r="E68">
-        <v>-17.15100415066408</v>
+        <v>-18.54742703803934</v>
       </c>
       <c r="F68">
-        <v>-1.898324992403384</v>
+        <v>-1.15429781671991</v>
       </c>
       <c r="G68">
-        <v>-8.195346017863718</v>
+        <v>-7.606985932987825</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-1.305700758526016</v>
       </c>
       <c r="E69">
-        <v>-17.61839700994375</v>
+        <v>-18.46744060164187</v>
       </c>
       <c r="F69">
-        <v>-1.001642129895003</v>
+        <v>-1.271596297691125</v>
       </c>
       <c r="G69">
-        <v>-8.564276523305638</v>
+        <v>-7.653211080352668</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-1.324247456487705</v>
       </c>
       <c r="E70">
-        <v>-17.76902764086089</v>
+        <v>-17.06909311281333</v>
       </c>
       <c r="F70">
-        <v>-1.113155292925067</v>
+        <v>-1.198004137626417</v>
       </c>
       <c r="G70">
-        <v>-8.78420930566158</v>
+        <v>-8.225690478276677</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-1.335996763335209</v>
       </c>
       <c r="E71">
-        <v>-18.33190337459229</v>
+        <v>-17.95210025956898</v>
       </c>
       <c r="F71">
-        <v>-1.523955941851786</v>
+        <v>-1.312014000008519</v>
       </c>
       <c r="G71">
-        <v>-8.059451434022176</v>
+        <v>-7.809511866898279</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-1.336694702508054</v>
       </c>
       <c r="E72">
-        <v>-15.75308233839227</v>
+        <v>-19.17038203643051</v>
       </c>
       <c r="F72">
-        <v>-1.901029611973524</v>
+        <v>-1.191139456959418</v>
       </c>
       <c r="G72">
-        <v>-7.758668508506152</v>
+        <v>-7.658848939406047</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-1.324418316590005</v>
       </c>
       <c r="E73">
-        <v>-18.67739877053349</v>
+        <v>-19.17182661963896</v>
       </c>
       <c r="F73">
-        <v>-1.31068281359222</v>
+        <v>-1.302281511393027</v>
       </c>
       <c r="G73">
-        <v>-8.005446504640044</v>
+        <v>-7.455912497848724</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-1.295475869410828</v>
       </c>
       <c r="E74">
-        <v>-18.26798849244803</v>
+        <v>-18.14665708836052</v>
       </c>
       <c r="F74">
-        <v>-2.089901521648825</v>
+        <v>-1.599609908382062</v>
       </c>
       <c r="G74">
-        <v>-7.700710787750131</v>
+        <v>-7.018109403007805</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-1.247251357102761</v>
       </c>
       <c r="E75">
-        <v>-19.1847825837749</v>
+        <v>-18.77844713954065</v>
       </c>
       <c r="F75">
-        <v>-1.44805926367249</v>
+        <v>-1.70192487977144</v>
       </c>
       <c r="G75">
-        <v>-7.076514047411627</v>
+        <v>-7.36408127513488</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-1.177809345621334</v>
       </c>
       <c r="E76">
-        <v>-17.67158846563785</v>
+        <v>-19.89157322147007</v>
       </c>
       <c r="F76">
-        <v>-2.199415834135934</v>
+        <v>-1.631070473972985</v>
       </c>
       <c r="G76">
-        <v>-7.823333394524736</v>
+        <v>-7.278642715857369</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-1.085130833707151</v>
       </c>
       <c r="E77">
-        <v>-18.81753692717486</v>
+        <v>-19.49630536771056</v>
       </c>
       <c r="F77">
-        <v>-2.251553278468135</v>
+        <v>-1.957360252098696</v>
       </c>
       <c r="G77">
-        <v>-7.763329756625446</v>
+        <v>-6.950716627464861</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-0.9687940533895643</v>
       </c>
       <c r="E78">
-        <v>-19.63629861318368</v>
+        <v>-19.84771042223177</v>
       </c>
       <c r="F78">
-        <v>-2.449761717140389</v>
+        <v>-1.919974374475549</v>
       </c>
       <c r="G78">
-        <v>-7.208293623147856</v>
+        <v>-7.168027457753701</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-0.8283473714004471</v>
       </c>
       <c r="E79">
-        <v>-18.25329359429314</v>
+        <v>-20.38092917968694</v>
       </c>
       <c r="F79">
-        <v>-1.913098925032313</v>
+        <v>-2.475539682348107</v>
       </c>
       <c r="G79">
-        <v>-5.966743040100522</v>
+        <v>-6.666747962742797</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-0.6646820858245823</v>
       </c>
       <c r="E80">
-        <v>-19.59733109434768</v>
+        <v>-19.98395409122654</v>
       </c>
       <c r="F80">
-        <v>-2.690105063756041</v>
+        <v>-2.040500174848071</v>
       </c>
       <c r="G80">
-        <v>-6.352868519073417</v>
+        <v>-6.173102585745452</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-0.4798300537639854</v>
       </c>
       <c r="E81">
-        <v>-19.77120185387218</v>
+        <v>-20.77419544793506</v>
       </c>
       <c r="F81">
-        <v>-2.514460524768642</v>
+        <v>-2.323156528398721</v>
       </c>
       <c r="G81">
-        <v>-6.659309166916055</v>
+        <v>-6.38492453153018</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-0.2768630314122286</v>
       </c>
       <c r="E82">
-        <v>-21.6896717533257</v>
+        <v>-22.55589184693491</v>
       </c>
       <c r="F82">
-        <v>-2.702552940717909</v>
+        <v>-2.493768735414113</v>
       </c>
       <c r="G82">
-        <v>-6.220466560775805</v>
+        <v>-6.65306216748345</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-0.05987050460756175</v>
       </c>
       <c r="E83">
-        <v>-21.27542506500005</v>
+        <v>-23.27145866725694</v>
       </c>
       <c r="F83">
-        <v>-3.393737731409399</v>
+        <v>-1.862897375320454</v>
       </c>
       <c r="G83">
-        <v>-5.764402496740267</v>
+        <v>-5.938315385554801</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>0.1659983869746135</v>
       </c>
       <c r="E84">
-        <v>-21.32437334054896</v>
+        <v>-22.9618967125666</v>
       </c>
       <c r="F84">
-        <v>-2.780138660031513</v>
+        <v>-2.418370734411302</v>
       </c>
       <c r="G84">
-        <v>-5.574711547885568</v>
+        <v>-6.321491168452205</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>0.3956149416219184</v>
       </c>
       <c r="E85">
-        <v>-23.04373076635921</v>
+        <v>-23.36456409285464</v>
       </c>
       <c r="F85">
-        <v>-2.700558232011967</v>
+        <v>-2.397693855670024</v>
       </c>
       <c r="G85">
-        <v>-5.433530022817808</v>
+        <v>-6.227855698419458</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>0.6228139114659135</v>
       </c>
       <c r="E86">
-        <v>-23.52971753991438</v>
+        <v>-24.09991128764218</v>
       </c>
       <c r="F86">
-        <v>-2.561196185267187</v>
+        <v>-2.258317726679396</v>
       </c>
       <c r="G86">
-        <v>-6.843776074909784</v>
+        <v>-5.630633283134936</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>0.8415537477373829</v>
       </c>
       <c r="E87">
-        <v>-24.68806949175841</v>
+        <v>-24.8536123875828</v>
       </c>
       <c r="F87">
-        <v>-3.187248103811358</v>
+        <v>-2.475719438074515</v>
       </c>
       <c r="G87">
-        <v>-5.575982797372648</v>
+        <v>-6.036655140798851</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>1.044785696364929</v>
       </c>
       <c r="E88">
-        <v>-25.0967325716326</v>
+        <v>-25.34555410445806</v>
       </c>
       <c r="F88">
-        <v>-3.347614234421523</v>
+        <v>-2.646963689418242</v>
       </c>
       <c r="G88">
-        <v>-5.938987426299272</v>
+        <v>-5.98442466382577</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>1.224746483243338</v>
       </c>
       <c r="E89">
-        <v>-27.27429005448696</v>
+        <v>-27.16298016337842</v>
       </c>
       <c r="F89">
-        <v>-3.52786532453589</v>
+        <v>-2.818521063640228</v>
       </c>
       <c r="G89">
-        <v>-6.346585103639881</v>
+        <v>-5.56284324212728</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>1.376754034165485</v>
       </c>
       <c r="E90">
-        <v>-27.6526893425679</v>
+        <v>-28.38801389498539</v>
       </c>
       <c r="F90">
-        <v>-3.449674897018242</v>
+        <v>-2.678551823589196</v>
       </c>
       <c r="G90">
-        <v>-6.251188423380242</v>
+        <v>-6.120143788753731</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>1.49637717852432</v>
       </c>
       <c r="E91">
-        <v>-31.03981581829303</v>
+        <v>-29.23879642070245</v>
       </c>
       <c r="F91">
-        <v>-3.621171800419823</v>
+        <v>-2.816362338188533</v>
       </c>
       <c r="G91">
-        <v>-5.561760693735939</v>
+        <v>-5.940804915800332</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>1.58297433988786</v>
       </c>
       <c r="E92">
-        <v>-30.91635376718491</v>
+        <v>-31.92010588064407</v>
       </c>
       <c r="F92">
-        <v>-3.314726391795577</v>
+        <v>-3.100978609014207</v>
       </c>
       <c r="G92">
-        <v>-6.147144598172027</v>
+        <v>-6.313982851169138</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>1.638274881063635</v>
       </c>
       <c r="E93">
-        <v>-32.69279487209886</v>
+        <v>-32.26777720834596</v>
       </c>
       <c r="F93">
-        <v>-3.202544736271454</v>
+        <v>-2.897920079198561</v>
       </c>
       <c r="G93">
-        <v>-6.873316072756701</v>
+        <v>-6.767266056951688</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>1.664982764469328</v>
       </c>
       <c r="E94">
-        <v>-34.58028774510291</v>
+        <v>-34.17744149009156</v>
       </c>
       <c r="F94">
-        <v>-4.078524212281667</v>
+        <v>-3.159462176019255</v>
       </c>
       <c r="G94">
-        <v>-6.792833400151479</v>
+        <v>-6.553087002742999</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>1.670409003140905</v>
       </c>
       <c r="E95">
-        <v>-35.86648983936848</v>
+        <v>-35.73918990653886</v>
       </c>
       <c r="F95">
-        <v>-3.178989280805447</v>
+        <v>-3.463601409794107</v>
       </c>
       <c r="G95">
-        <v>-7.026140786486077</v>
+        <v>-6.922769002022334</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>1.663050413176438</v>
       </c>
       <c r="E96">
-        <v>-38.9178526097949</v>
+        <v>-37.67429741949656</v>
       </c>
       <c r="F96">
-        <v>-4.174465724873905</v>
+        <v>-3.335945851185689</v>
       </c>
       <c r="G96">
-        <v>-6.912618869398929</v>
+        <v>-6.404076037474864</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>1.65005625645933</v>
       </c>
       <c r="E97">
-        <v>-38.07016756029908</v>
+        <v>-39.73383154852601</v>
       </c>
       <c r="F97">
-        <v>-4.39015271574523</v>
+        <v>-3.290578653636569</v>
       </c>
       <c r="G97">
-        <v>-8.319183594851236</v>
+        <v>-7.177902815097347</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>1.643389217469872</v>
       </c>
       <c r="E98">
-        <v>-40.68280044767738</v>
+        <v>-41.42624908246464</v>
       </c>
       <c r="F98">
-        <v>-3.998409487287315</v>
+        <v>-3.609639269438049</v>
       </c>
       <c r="G98">
-        <v>-8.198941270319366</v>
+        <v>-7.441538109117208</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>1.644946193572919</v>
       </c>
       <c r="E99">
-        <v>-43.15841529700559</v>
+        <v>-43.77814375766629</v>
       </c>
       <c r="F99">
-        <v>-4.7535359578009</v>
+        <v>-3.654670978189035</v>
       </c>
       <c r="G99">
-        <v>-8.149461856689419</v>
+        <v>-7.940953766989502</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>1.666163660383569</v>
       </c>
       <c r="E100">
-        <v>-45.683741469753</v>
+        <v>-46.12069619099012</v>
       </c>
       <c r="F100">
-        <v>-3.981830542087686</v>
+        <v>-3.861961637065584</v>
       </c>
       <c r="G100">
-        <v>-8.187168970381718</v>
+        <v>-8.40192405951424</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>1.69869297666745</v>
       </c>
       <c r="E101">
-        <v>-49.22220048986647</v>
+        <v>-46.97270366892626</v>
       </c>
       <c r="F101">
-        <v>-4.652478448128972</v>
+        <v>-3.858185938443623</v>
       </c>
       <c r="G101">
-        <v>-7.81791072093141</v>
+        <v>-8.429212886394453</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>1.753530011805783</v>
       </c>
       <c r="E102">
-        <v>-48.70329963510505</v>
+        <v>-49.45410477591777</v>
       </c>
       <c r="F102">
-        <v>-4.986805875164046</v>
+        <v>-3.913519224215825</v>
       </c>
       <c r="G102">
-        <v>-8.477709067999236</v>
+        <v>-8.382219692464497</v>
       </c>
     </row>
   </sheetData>
